--- a/data_modelos/4_Relacion_modelos_activos_e_indicadores.xlsx
+++ b/data_modelos/4_Relacion_modelos_activos_e_indicadores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29929484-4F8F-4B1B-903C-1462A2382C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAAC5A0C-3FB4-4F16-871A-F74318036DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34770" yWindow="2910" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Relación" sheetId="1" r:id="rId1"/>
@@ -643,6 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:T55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -721,7 +722,7 @@
       <c r="S1" s="7"/>
       <c r="T1" s="7"/>
     </row>
-    <row r="2" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -757,7 +758,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -847,7 +848,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>30</v>
       </c>
@@ -901,7 +902,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -937,7 +938,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -1027,7 +1028,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
@@ -1081,7 +1082,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:20" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" s="1" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1117,7 +1118,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -1153,7 +1154,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
@@ -1189,7 +1190,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1225,7 +1226,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:20" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" s="1" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1261,7 +1262,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
@@ -1351,7 +1352,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>30</v>
       </c>
@@ -1405,7 +1406,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>9</v>
       </c>
@@ -1441,7 +1442,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>9</v>
       </c>
@@ -1477,7 +1478,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>9</v>
       </c>
@@ -1513,7 +1514,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>9</v>
       </c>
@@ -1603,7 +1604,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
@@ -1657,7 +1658,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>9</v>
       </c>
@@ -1693,7 +1694,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
@@ -1729,7 +1730,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>9</v>
       </c>
@@ -1765,7 +1766,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>9</v>
       </c>
@@ -1855,7 +1856,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
@@ -1909,7 +1910,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>9</v>
       </c>
@@ -1945,7 +1946,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>9</v>
       </c>
@@ -1981,7 +1982,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>9</v>
       </c>
@@ -2017,7 +2018,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>9</v>
       </c>
@@ -2053,7 +2054,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>9</v>
       </c>
@@ -2089,7 +2090,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>9</v>
       </c>
@@ -2125,7 +2126,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>9</v>
       </c>
@@ -2161,7 +2162,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>9</v>
       </c>
@@ -2197,7 +2198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>55</v>
       </c>
@@ -2224,7 +2225,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>9</v>
       </c>
@@ -2243,12 +2244,14 @@
       <c r="H39" s="1"/>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
       <c r="B40" s="10" t="s">
         <v>47</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>20</v>
       </c>
+      <c r="D40" s="1"/>
       <c r="E40" s="2" t="s">
         <v>13</v>
       </c>
@@ -2257,7 +2260,7 @@
       </c>
       <c r="H40" s="1"/>
     </row>
-    <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="10" t="s">
         <v>47</v>
       </c>
@@ -2272,7 +2275,7 @@
       </c>
       <c r="H41" s="1"/>
     </row>
-    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>55</v>
       </c>
@@ -2299,7 +2302,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>9</v>
       </c>
@@ -2318,12 +2321,14 @@
       <c r="H43" s="1"/>
     </row>
     <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
       <c r="B44" s="10" t="s">
         <v>48</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>20</v>
       </c>
+      <c r="D44" s="1"/>
       <c r="E44" s="2" t="s">
         <v>13</v>
       </c>
@@ -2332,7 +2337,7 @@
       </c>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="10" t="s">
         <v>48</v>
       </c>
@@ -2347,7 +2352,7 @@
       </c>
       <c r="H45" s="1"/>
     </row>
-    <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>55</v>
       </c>
@@ -2374,7 +2379,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>9</v>
       </c>
@@ -2393,12 +2398,14 @@
       <c r="H47" s="1"/>
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
       <c r="B48" s="10" t="s">
         <v>49</v>
       </c>
       <c r="C48" s="11" t="s">
         <v>20</v>
       </c>
+      <c r="D48" s="1"/>
       <c r="E48" s="2" t="s">
         <v>13</v>
       </c>
@@ -2407,7 +2414,7 @@
       </c>
       <c r="H48" s="1"/>
     </row>
-    <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="10" t="s">
         <v>49</v>
       </c>
@@ -2422,7 +2429,7 @@
       </c>
       <c r="H49" s="1"/>
     </row>
-    <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>9</v>
       </c>
@@ -2441,12 +2448,14 @@
       <c r="H50" s="1"/>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
       <c r="B51" s="10" t="s">
         <v>50</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>20</v>
       </c>
+      <c r="D51" s="1"/>
       <c r="E51" s="2" t="s">
         <v>13</v>
       </c>
@@ -2455,7 +2464,7 @@
       </c>
       <c r="H51" s="1"/>
     </row>
-    <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="10" t="s">
         <v>50</v>
       </c>
@@ -2470,7 +2479,7 @@
       </c>
       <c r="H52" s="1"/>
     </row>
-    <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>55</v>
       </c>
@@ -2497,7 +2506,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>9</v>
       </c>
@@ -2515,7 +2524,7 @@
       </c>
       <c r="H54" s="1"/>
     </row>
-    <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="10" t="s">
         <v>51</v>
       </c>
@@ -2531,7 +2540,13 @@
       <c r="H55" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T55" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T55" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="OPEX falta de calado"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G55" xr:uid="{18612B50-46E6-4B80-8E9F-A7A3D5687779}">

--- a/data_modelos/4_Relacion_modelos_activos_e_indicadores.xlsx
+++ b/data_modelos/4_Relacion_modelos_activos_e_indicadores.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4A813C-AFAD-4F13-8F7B-70C61886BDC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$67</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="90">
   <si>
     <t>Modelo</t>
   </si>
@@ -289,8 +303,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,21 +333,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -371,7 +394,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -405,6 +428,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -439,9 +463,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -614,11 +639,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q67"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="181.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="34.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -671,7 +712,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -706,7 +747,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -741,7 +782,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -794,7 +835,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -847,7 +888,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -882,7 +923,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -917,7 +958,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -970,7 +1011,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1023,7 +1064,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1058,7 +1099,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1093,7 +1134,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -1128,7 +1169,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1163,7 +1204,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1198,7 +1239,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1233,7 +1274,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1286,7 +1327,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:17">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1339,7 +1380,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1374,7 +1415,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:17">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1409,7 +1450,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1444,7 +1485,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -1479,7 +1520,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -1532,7 +1573,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -1585,7 +1626,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -1620,7 +1661,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -1655,7 +1696,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -1690,7 +1731,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -1725,7 +1766,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -1778,7 +1819,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>19</v>
       </c>
@@ -1831,7 +1872,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:17">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -1866,7 +1907,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:17">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -1901,7 +1942,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="1:17">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -1936,7 +1977,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -1971,7 +2012,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -2006,7 +2047,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -2041,7 +2082,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -2076,7 +2117,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -2111,7 +2152,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>20</v>
       </c>
@@ -2137,7 +2178,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>20</v>
       </c>
@@ -2163,7 +2204,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -2189,7 +2230,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -2215,11 +2256,11 @@
         <v>79</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>17</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C42" t="s">
@@ -2241,7 +2282,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>17</v>
       </c>
@@ -2267,7 +2308,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -2293,7 +2334,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -2319,7 +2360,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -2345,7 +2386,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -2371,7 +2412,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>17</v>
       </c>
@@ -2397,7 +2438,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>17</v>
       </c>
@@ -2423,7 +2464,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>17</v>
       </c>
@@ -2449,18 +2490,18 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>17</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D51" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E51" t="s">
         <v>73</v>
@@ -2469,24 +2510,30 @@
         <v>76</v>
       </c>
       <c r="G51" t="s">
-        <v>78</v>
+        <v>77</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+        <v>68</v>
+      </c>
+      <c r="J51" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>17</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C52" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D52" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E52" t="s">
         <v>73</v>
@@ -2495,24 +2542,30 @@
         <v>76</v>
       </c>
       <c r="G52" t="s">
-        <v>78</v>
+        <v>77</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
       </c>
       <c r="I52" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+        <v>68</v>
+      </c>
+      <c r="J52" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>17</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C53" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D53" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E53" t="s">
         <v>73</v>
@@ -2521,13 +2574,19 @@
         <v>76</v>
       </c>
       <c r="G53" t="s">
-        <v>78</v>
+        <v>77</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
+        <v>68</v>
+      </c>
+      <c r="J53" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -2553,7 +2612,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>17</v>
       </c>
@@ -2579,7 +2638,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -2605,7 +2664,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -2631,7 +2690,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -2657,7 +2716,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -2683,7 +2742,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -2709,7 +2768,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -2735,7 +2794,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -2761,7 +2820,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>17</v>
       </c>
@@ -2787,7 +2846,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -2813,7 +2872,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>17</v>
       </c>
@@ -2839,7 +2898,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -2865,7 +2924,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -2892,6 +2951,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q67" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data_modelos/4_Relacion_modelos_activos_e_indicadores.xlsx
+++ b/data_modelos/4_Relacion_modelos_activos_e_indicadores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4A813C-AFAD-4F13-8F7B-70C61886BDC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CF120B-285C-4F27-BE66-DEFE9295D231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="92">
   <si>
     <t>Modelo</t>
   </si>
@@ -298,6 +298,12 @@
   </si>
   <si>
     <t>Tasa de sedimentación anual (m/año)</t>
+  </si>
+  <si>
+    <t>Número de días ventosos</t>
+  </si>
+  <si>
+    <t>Personal del puerto</t>
   </si>
 </sst>
 </file>
@@ -321,7 +327,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -329,13 +335,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -640,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -2872,7 +2896,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>17</v>
       </c>
@@ -2898,7 +2922,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -2924,7 +2948,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -2948,6 +2972,38 @@
       </c>
       <c r="I67" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>17</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C68" t="s">
+        <v>60</v>
+      </c>
+      <c r="D68" t="s">
+        <v>68</v>
+      </c>
+      <c r="E68" t="s">
+        <v>73</v>
+      </c>
+      <c r="F68" t="s">
+        <v>76</v>
+      </c>
+      <c r="G68" t="s">
+        <v>77</v>
+      </c>
+      <c r="H68">
+        <v>1</v>
+      </c>
+      <c r="I68" t="s">
+        <v>68</v>
+      </c>
+      <c r="J68" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/data_modelos/4_Relacion_modelos_activos_e_indicadores.xlsx
+++ b/data_modelos/4_Relacion_modelos_activos_e_indicadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CF120B-285C-4F27-BE66-DEFE9295D231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEEECCBB-8893-4704-B0F7-7F6143F015E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,10 +16,21 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$69</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -28,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="97">
   <si>
     <t>Modelo</t>
   </si>
@@ -304,6 +315,21 @@
   </si>
   <si>
     <t>Personal del puerto</t>
+  </si>
+  <si>
+    <t>Exceso de precipitación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precipitación </t>
+  </si>
+  <si>
+    <t>Precipitacion</t>
+  </si>
+  <si>
+    <t>Número de días al año con precipitación ≥ 1 mm</t>
+  </si>
+  <si>
+    <t>Número de días al año con precipitación ≥ 20 mm</t>
   </si>
 </sst>
 </file>
@@ -664,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:Q69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -759,6 +785,7 @@
         <v>77</v>
       </c>
       <c r="H2">
+        <f>IF(COUNTA(I2:Q2)&lt;3,"",COUNTA(I2:Q2)/3)</f>
         <v>1</v>
       </c>
       <c r="I2" t="s">
@@ -794,6 +821,7 @@
         <v>77</v>
       </c>
       <c r="H3">
+        <f t="shared" ref="H3:H66" si="0">IF(COUNTA(I3:Q3)&lt;3,"",COUNTA(I3:Q3)/3)</f>
         <v>1</v>
       </c>
       <c r="I3" t="s">
@@ -829,6 +857,7 @@
         <v>77</v>
       </c>
       <c r="H4">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="I4" t="s">
@@ -882,6 +911,7 @@
         <v>77</v>
       </c>
       <c r="H5">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="I5" t="s">
@@ -935,6 +965,7 @@
         <v>77</v>
       </c>
       <c r="H6">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I6" t="s">
@@ -970,6 +1001,7 @@
         <v>77</v>
       </c>
       <c r="H7">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I7" t="s">
@@ -1005,6 +1037,7 @@
         <v>77</v>
       </c>
       <c r="H8">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="I8" t="s">
@@ -1058,6 +1091,7 @@
         <v>77</v>
       </c>
       <c r="H9">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="I9" t="s">
@@ -1111,6 +1145,7 @@
         <v>77</v>
       </c>
       <c r="H10">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I10" t="s">
@@ -1146,6 +1181,7 @@
         <v>77</v>
       </c>
       <c r="H11">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I11" t="s">
@@ -1181,6 +1217,7 @@
         <v>77</v>
       </c>
       <c r="H12">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I12" t="s">
@@ -1216,6 +1253,7 @@
         <v>77</v>
       </c>
       <c r="H13">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I13" t="s">
@@ -1251,6 +1289,7 @@
         <v>77</v>
       </c>
       <c r="H14">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I14" t="s">
@@ -1286,6 +1325,7 @@
         <v>77</v>
       </c>
       <c r="H15">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I15" t="s">
@@ -1321,6 +1361,7 @@
         <v>77</v>
       </c>
       <c r="H16">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="I16" t="s">
@@ -1374,6 +1415,7 @@
         <v>77</v>
       </c>
       <c r="H17">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="I17" t="s">
@@ -1427,6 +1469,7 @@
         <v>77</v>
       </c>
       <c r="H18">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I18" t="s">
@@ -1462,6 +1505,7 @@
         <v>77</v>
       </c>
       <c r="H19">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I19" t="s">
@@ -1497,6 +1541,7 @@
         <v>77</v>
       </c>
       <c r="H20">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I20" t="s">
@@ -1532,6 +1577,7 @@
         <v>77</v>
       </c>
       <c r="H21">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I21" t="s">
@@ -1567,6 +1613,7 @@
         <v>77</v>
       </c>
       <c r="H22">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="I22" t="s">
@@ -1620,6 +1667,7 @@
         <v>77</v>
       </c>
       <c r="H23">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="I23" t="s">
@@ -1673,6 +1721,7 @@
         <v>77</v>
       </c>
       <c r="H24">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I24" t="s">
@@ -1708,6 +1757,7 @@
         <v>77</v>
       </c>
       <c r="H25">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I25" t="s">
@@ -1743,6 +1793,7 @@
         <v>77</v>
       </c>
       <c r="H26">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I26" t="s">
@@ -1778,6 +1829,7 @@
         <v>77</v>
       </c>
       <c r="H27">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I27" t="s">
@@ -1813,6 +1865,7 @@
         <v>77</v>
       </c>
       <c r="H28">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="I28" t="s">
@@ -1866,6 +1919,7 @@
         <v>77</v>
       </c>
       <c r="H29">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="I29" t="s">
@@ -1919,6 +1973,7 @@
         <v>77</v>
       </c>
       <c r="H30">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I30" t="s">
@@ -1954,6 +2009,7 @@
         <v>77</v>
       </c>
       <c r="H31">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I31" t="s">
@@ -1989,6 +2045,7 @@
         <v>77</v>
       </c>
       <c r="H32">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I32" t="s">
@@ -2024,6 +2081,7 @@
         <v>77</v>
       </c>
       <c r="H33">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I33" t="s">
@@ -2059,6 +2117,7 @@
         <v>77</v>
       </c>
       <c r="H34">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I34" t="s">
@@ -2094,6 +2153,7 @@
         <v>77</v>
       </c>
       <c r="H35">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I35" t="s">
@@ -2129,6 +2189,7 @@
         <v>77</v>
       </c>
       <c r="H36">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I36" t="s">
@@ -2164,6 +2225,7 @@
         <v>77</v>
       </c>
       <c r="H37">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I37" t="s">
@@ -2198,6 +2260,10 @@
       <c r="G38" t="s">
         <v>78</v>
       </c>
+      <c r="H38" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I38" t="s">
         <v>79</v>
       </c>
@@ -2224,6 +2290,10 @@
       <c r="G39" t="s">
         <v>78</v>
       </c>
+      <c r="H39" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I39" t="s">
         <v>79</v>
       </c>
@@ -2250,6 +2320,10 @@
       <c r="G40" t="s">
         <v>78</v>
       </c>
+      <c r="H40" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I40" t="s">
         <v>79</v>
       </c>
@@ -2276,6 +2350,10 @@
       <c r="G41" t="s">
         <v>78</v>
       </c>
+      <c r="H41" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I41" t="s">
         <v>79</v>
       </c>
@@ -2302,6 +2380,10 @@
       <c r="G42" t="s">
         <v>78</v>
       </c>
+      <c r="H42" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I42" t="s">
         <v>79</v>
       </c>
@@ -2328,6 +2410,10 @@
       <c r="G43" t="s">
         <v>78</v>
       </c>
+      <c r="H43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I43" t="s">
         <v>79</v>
       </c>
@@ -2354,6 +2440,10 @@
       <c r="G44" t="s">
         <v>78</v>
       </c>
+      <c r="H44" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I44" t="s">
         <v>79</v>
       </c>
@@ -2380,6 +2470,10 @@
       <c r="G45" t="s">
         <v>78</v>
       </c>
+      <c r="H45" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I45" t="s">
         <v>79</v>
       </c>
@@ -2406,6 +2500,10 @@
       <c r="G46" t="s">
         <v>78</v>
       </c>
+      <c r="H46" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I46" t="s">
         <v>79</v>
       </c>
@@ -2432,6 +2530,10 @@
       <c r="G47" t="s">
         <v>78</v>
       </c>
+      <c r="H47" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I47" t="s">
         <v>79</v>
       </c>
@@ -2458,11 +2560,15 @@
       <c r="G48" t="s">
         <v>78</v>
       </c>
+      <c r="H48" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I48" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>17</v>
       </c>
@@ -2484,11 +2590,15 @@
       <c r="G49" t="s">
         <v>78</v>
       </c>
+      <c r="H49" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I49" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>17</v>
       </c>
@@ -2510,11 +2620,15 @@
       <c r="G50" t="s">
         <v>78</v>
       </c>
+      <c r="H50" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I50" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>17</v>
       </c>
@@ -2537,6 +2651,7 @@
         <v>77</v>
       </c>
       <c r="H51">
+        <f>IF(COUNTA(I51:Q51)&lt;3,"",COUNTA(I51:Q51)/3)</f>
         <v>1</v>
       </c>
       <c r="I51" t="s">
@@ -2545,8 +2660,11 @@
       <c r="J51" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K51" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>17</v>
       </c>
@@ -2569,6 +2687,7 @@
         <v>77</v>
       </c>
       <c r="H52">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I52" t="s">
@@ -2577,8 +2696,11 @@
       <c r="J52" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K52" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>17</v>
       </c>
@@ -2601,6 +2723,7 @@
         <v>77</v>
       </c>
       <c r="H53">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I53" t="s">
@@ -2609,8 +2732,11 @@
       <c r="J53" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K53" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -2632,11 +2758,15 @@
       <c r="G54" t="s">
         <v>78</v>
       </c>
+      <c r="H54" t="str">
+        <f>IF(COUNTA(I54:Q54)&lt;3,"",COUNTA(I54:Q54)/3)</f>
+        <v/>
+      </c>
       <c r="I54" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>17</v>
       </c>
@@ -2658,11 +2788,15 @@
       <c r="G55" t="s">
         <v>78</v>
       </c>
+      <c r="H55" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I55" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -2684,11 +2818,15 @@
       <c r="G56" t="s">
         <v>78</v>
       </c>
+      <c r="H56" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I56" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -2710,11 +2848,15 @@
       <c r="G57" t="s">
         <v>78</v>
       </c>
+      <c r="H57" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I57" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -2736,11 +2878,15 @@
       <c r="G58" t="s">
         <v>78</v>
       </c>
+      <c r="H58" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I58" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -2762,11 +2908,15 @@
       <c r="G59" t="s">
         <v>78</v>
       </c>
+      <c r="H59" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I59" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -2788,11 +2938,15 @@
       <c r="G60" t="s">
         <v>78</v>
       </c>
+      <c r="H60" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I60" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -2814,11 +2968,15 @@
       <c r="G61" t="s">
         <v>78</v>
       </c>
+      <c r="H61" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I61" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -2840,11 +2998,15 @@
       <c r="G62" t="s">
         <v>78</v>
       </c>
+      <c r="H62" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I62" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>17</v>
       </c>
@@ -2866,11 +3028,15 @@
       <c r="G63" t="s">
         <v>78</v>
       </c>
+      <c r="H63" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I63" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -2892,11 +3058,15 @@
       <c r="G64" t="s">
         <v>78</v>
       </c>
+      <c r="H64" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I64" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>17</v>
       </c>
@@ -2918,11 +3088,15 @@
       <c r="G65" t="s">
         <v>78</v>
       </c>
+      <c r="H65" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I65" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -2944,11 +3118,15 @@
       <c r="G66" t="s">
         <v>78</v>
       </c>
+      <c r="H66" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="I66" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -2970,11 +3148,15 @@
       <c r="G67" t="s">
         <v>78</v>
       </c>
+      <c r="H67" t="str">
+        <f t="shared" ref="H67:H69" si="1">IF(COUNTA(I67:Q67)&lt;3,"",COUNTA(I67:Q67)/3)</f>
+        <v/>
+      </c>
       <c r="I67" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>17</v>
       </c>
@@ -2997,6 +3179,7 @@
         <v>77</v>
       </c>
       <c r="H68">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I68" t="s">
@@ -3005,9 +3188,56 @@
       <c r="J68" t="s">
         <v>90</v>
       </c>
+      <c r="K68" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>17</v>
+      </c>
+      <c r="B69" t="s">
+        <v>43</v>
+      </c>
+      <c r="C69" t="s">
+        <v>92</v>
+      </c>
+      <c r="D69" t="s">
+        <v>93</v>
+      </c>
+      <c r="E69" t="s">
+        <v>73</v>
+      </c>
+      <c r="F69" t="s">
+        <v>76</v>
+      </c>
+      <c r="G69" t="s">
+        <v>77</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="I69" t="s">
+        <v>94</v>
+      </c>
+      <c r="J69" t="s">
+        <v>95</v>
+      </c>
+      <c r="K69" t="s">
+        <v>95</v>
+      </c>
+      <c r="L69" t="s">
+        <v>94</v>
+      </c>
+      <c r="M69" t="s">
+        <v>96</v>
+      </c>
+      <c r="N69" t="s">
+        <v>96</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q67" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data_modelos/4_Relacion_modelos_activos_e_indicadores.xlsx
+++ b/data_modelos/4_Relacion_modelos_activos_e_indicadores.xlsx
@@ -4355,7 +4355,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>P98</t>
+          <t>P99</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
